--- a/01.엑셀자동화기초/data2/250617_Data_form2.xlsx
+++ b/01.엑셀자동화기초/data2/250617_Data_form2.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlcn.WorksheetConnection_Sheet1B3AI1081" hidden="1">Sheet1!$A$1:$AG$104</definedName>
     <definedName name="_xlcn.WorksheetConnection_Sheet3Y1Y211" hidden="1">Sheet3!$Y$1:$Y$21</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1446,7 +1446,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -2446,7 +2446,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
@@ -2507,6 +2507,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2523,6 +2528,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -2539,6 +2549,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -2555,6 +2570,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -2571,6 +2591,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -2587,6 +2612,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -2603,6 +2633,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -2619,6 +2654,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -2635,6 +2675,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -2651,6 +2696,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -2847,6 +2897,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000014-D9DA-4D13-890B-C1525E5F10B9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2937,6 +2992,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000016-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -2967,6 +3027,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000018-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
@@ -2997,6 +3062,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001A-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3195,6 +3265,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001B-D9DA-4D13-890B-C1525E5F10B9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -3660,7 +3735,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
@@ -3706,6 +3781,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet3!$M$2:$M$21</c:f>
@@ -3843,6 +3976,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0F5A-42D2-863E-49B390622644}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -3904,6 +4042,64 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet3!$M$2:$M$21</c:f>
@@ -4042,6 +4238,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0F5A-42D2-863E-49B390622644}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -4175,6 +4376,8 @@
         <c:axId val="1299089904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="190"/>
+          <c:min val="50"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -4506,7 +4709,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
@@ -4567,6 +4770,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -4583,6 +4791,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -4599,6 +4812,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -4615,6 +4833,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -4631,6 +4854,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -4647,6 +4875,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -4663,6 +4896,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -4679,6 +4917,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -4695,6 +4938,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -4711,6 +4959,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-78EC-4030-B10B-FA43034E1A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -4907,6 +5160,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000014-78EC-4030-B10B-FA43034E1A8E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -5165,6 +5423,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000015-78EC-4030-B10B-FA43034E1A8E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -5629,6 +5892,860 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>하부소재</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:marker>
+              <c:symbol val="square"/>
+              <c:size val="8"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:ln w="19050">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="00B050"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+                <a:tailEnd type="arrow"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.2331414392034604E-2"/>
+                  <c:y val="0.10275490524759019"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ko-KR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Sheet3!$AN$7:$AN$11,Sheet3!$AN$17:$AN$21)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>317</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Sheet3!$Y$7:$Y$11,Sheet3!$Y$17:$Y$21)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>184.529</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>159.459</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>158.24799999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>171.202</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170.084</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>179.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>180.149</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>174.744</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>184.995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>168.59299999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000014-D9DA-4D13-890B-C1525E5F10B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>상부소재</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:ln w="44450">
+                <a:noFill/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="9"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:ln w="44450">
+                  <a:noFill/>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:noFill/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000016-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0070C0"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+                <a:tailEnd type="arrow"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.6475407631543161E-3"/>
+                  <c:y val="-1.9028363154326249E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ko-KR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Sheet3!$AN$2:$AN$6,Sheet3!$AN$12:$AN$16)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>146</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Sheet3!$Y$2:$Y$6,Sheet3!$Y$12:$Y$16)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>178.37799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>159.739</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>160.48500000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>152.749</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155.35900000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>178.09899999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>172.227</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>179.404</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>174.744</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>184.90199999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001B-D9DA-4D13-890B-C1525E5F10B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1299088272"/>
+        <c:axId val="1299087728"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1299087728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+          <c:min val="140"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>압연부하</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>(%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" sz="1200">
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299088272"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1299088272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="180"/>
+          <c:min val="120"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>추출 후 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>6pass </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>도달시간</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>(</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>초</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299087728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
   <a:schemeClr val="accent1"/>
@@ -5642,6 +6759,12 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
   <a:schemeClr val="accent1"/>
 </cs:colorStyle>
@@ -7156,6 +8279,485 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -7243,6 +8845,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>57630</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>14088</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>328830</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>83053</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="차트 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -24397,7 +26029,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AV51"/>
+  <dimension ref="A1:AV71"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.3984375" style="61" bestFit="1" customWidth="1"/>
@@ -27504,23 +29136,37 @@
     <row r="26" spans="1:48" s="92" customFormat="1" x14ac:dyDescent="0.4"/>
     <row r="27" spans="1:48" s="92" customFormat="1" x14ac:dyDescent="0.4"/>
     <row r="28" spans="1:48" s="92" customFormat="1" x14ac:dyDescent="0.4"/>
-    <row r="50" spans="22:23" x14ac:dyDescent="0.4">
+    <row r="50" spans="22:34" x14ac:dyDescent="0.4">
       <c r="V50" s="61" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="51" spans="22:23" x14ac:dyDescent="0.4">
+    <row r="51" spans="22:34" x14ac:dyDescent="0.4">
       <c r="V51" s="61" t="s">
         <v>347</v>
       </c>
       <c r="W51" s="61" t="s">
         <v>348</v>
+      </c>
+    </row>
+    <row r="58" spans="22:34" x14ac:dyDescent="0.4">
+      <c r="AH58" s="61">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="34:35" x14ac:dyDescent="0.4">
+      <c r="AH71" s="61">
+        <v>1100</v>
+      </c>
+      <c r="AI71" s="42">
+        <f>+AH71*3000000</f>
+        <v>3300000000</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>

--- a/01.엑셀자동화기초/data2/250617_Data_form2.xlsx
+++ b/01.엑셀자동화기초/data2/250617_Data_form2.xlsx
@@ -6746,6 +6746,2179 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>상부소재</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:ln w="44450">
+                <a:noFill/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="9"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:ln w="44450">
+                  <a:noFill/>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:noFill/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000016-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+                <a:tailEnd type="arrow"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.6475407631543161E-3"/>
+                  <c:y val="-1.9028363154326249E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ko-KR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Sheet3!$AN$2:$AN$6,Sheet3!$AN$12:$AN$16)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>146</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Sheet3!$Y$2:$Y$6,Sheet3!$Y$12:$Y$16)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>178.37799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>159.739</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>160.48500000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>152.749</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155.35900000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>178.09899999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>172.227</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>179.404</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>174.744</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>184.90199999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001B-D9DA-4D13-890B-C1525E5F10B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1299088272"/>
+        <c:axId val="1299087728"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1299087728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+          <c:min val="140"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>압연부하</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>(%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" sz="1200">
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299088272"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1299088272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="180"/>
+          <c:min val="120"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>추출 후 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>6pass </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>도달시간</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>(</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>초</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299087728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>하부소재</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:marker>
+              <c:symbol val="square"/>
+              <c:size val="8"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:ln w="19050">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+                <a:tailEnd type="arrow"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.2331414392034604E-2"/>
+                  <c:y val="0.10275490524759019"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ko-KR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Sheet3!$AN$7:$AN$11,Sheet3!$AN$17:$AN$21)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>317</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Sheet3!$Y$7:$Y$11,Sheet3!$Y$17:$Y$21)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>184.529</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>159.459</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>158.24799999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>171.202</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170.084</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>179.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>180.149</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>174.744</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>184.995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>168.59299999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000014-D9DA-4D13-890B-C1525E5F10B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1299088272"/>
+        <c:axId val="1299087728"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1299087728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+          <c:min val="140"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>압연부하</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>(%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" sz="1200">
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299088272"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1299088272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="180"/>
+          <c:min val="120"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>추출 후 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>6pass </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>도달시간</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>(</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>초</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299087728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>상부소재</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:ln w="44450">
+                <a:noFill/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="9"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:ln w="44450">
+                  <a:noFill/>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:noFill/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000016-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+                <a:tailEnd type="arrow"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.6475407631543161E-3"/>
+                  <c:y val="-1.9028363154326249E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ko-KR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Sheet3!$AN$2:$AN$6,Sheet3!$AN$12:$AN$16)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>146</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Sheet3!$Y$2:$Y$6,Sheet3!$Y$12:$Y$16)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>178.37799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>159.739</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>160.48500000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>152.749</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155.35900000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>178.09899999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>172.227</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>179.404</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>174.744</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>184.90199999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001B-D9DA-4D13-890B-C1525E5F10B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1299088272"/>
+        <c:axId val="1299087728"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1299087728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+          <c:min val="140"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>압연부하</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>(%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" sz="1200">
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299088272"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1299088272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="180"/>
+          <c:min val="120"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>추출 후 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>6pass </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>도달시간</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>(</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>초</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299087728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>하부소재</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:marker>
+              <c:symbol val="square"/>
+              <c:size val="8"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:ln w="19050">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-D9DA-4D13-890B-C1525E5F10B9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+                <a:tailEnd type="arrow"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.2331414392034604E-2"/>
+                  <c:y val="0.10275490524759019"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ko-KR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Sheet3!$AN$7:$AN$11,Sheet3!$AN$17:$AN$21)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>317</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Sheet3!$Y$7:$Y$11,Sheet3!$Y$17:$Y$21)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>184.529</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>159.459</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>158.24799999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>171.202</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170.084</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>179.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>180.149</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>174.744</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>184.995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>168.59299999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000014-D9DA-4D13-890B-C1525E5F10B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1299088272"/>
+        <c:axId val="1299087728"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1299087728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+          <c:min val="140"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1299088272"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1299088272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="180"/>
+          <c:min val="120"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>추출 후 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>6pass </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>도달시간</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>(</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>초</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+                    <a:latin typeface="+mn-ea"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:rPr>
+                  <a:t>)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-ea"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299087728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
   <a:schemeClr val="accent1"/>
@@ -6765,6 +8938,30 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
   <a:schemeClr val="accent1"/>
 </cs:colorStyle>
@@ -8758,6 +10955,1922 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -8875,6 +12988,126 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>514830</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>94770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>1290917</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>163735</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="차트 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>532760</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>175452</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>1775011</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>20299</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="차트 6"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>317606</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>112699</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>1703293</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>181664</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="차트 7"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>1420265</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>139593</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>806823</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>208558</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="차트 8"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
